--- a/qwen_zeroshot_2000_sample/qwen_zeroshot_summary_metrics.xlsx
+++ b/qwen_zeroshot_2000_sample/qwen_zeroshot_summary_metrics.xlsx
@@ -450,31 +450,31 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>0.5907352315110196</v>
+        <v>0.6032282086238564</v>
       </c>
       <c r="B2">
-        <v>0.02285575939531382</v>
+        <v>0.02320723764640767</v>
       </c>
       <c r="C2">
-        <v>0.3295793195743171</v>
+        <v>0.2712039780574048</v>
       </c>
       <c r="D2">
-        <v>0.01230987302251114</v>
+        <v>0.01240595437535159</v>
       </c>
       <c r="E2">
-        <v>0.755052294103011</v>
+        <v>0.7969352671618057</v>
       </c>
       <c r="F2">
-        <v>0.02626231238142967</v>
+        <v>0.02667678180506059</v>
       </c>
       <c r="G2">
-        <v>0.3295793195743171</v>
+        <v>0.2712039780574048</v>
       </c>
       <c r="H2">
-        <v>0.01524951653447581</v>
+        <v>0.01443330290716652</v>
       </c>
       <c r="I2">
-        <v>0.7374711606712668</v>
+        <v>0.8083405565391627</v>
       </c>
       <c r="J2">
         <v>1999</v>
